--- a/plantilla-datos.xlsx
+++ b/plantilla-datos.xlsx
@@ -23,7 +23,7 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
-          <t>Criterio de compatibilidad de molde. Ej: 'Gris cemento gris'.</t>
+          <t>El color: Gris, Beige, Terracota. El cemento NO va acá: tiene su propia columna.</t>
         </r>
       </text>
     </comment>
@@ -106,6 +106,13 @@
     <comment ref="G1" authorId="0">
       <text>
         <r>
+          <t>gris o blanco. Vacío = gris. Uhma Beige con cemento gris y con cemento blanco son dos productos distintos.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
           <t>Decimal. Es lo que convierte toda la producción a m2.</t>
         </r>
       </text>
@@ -123,25 +130,32 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
-          <t>Identificador interno, único. Ej: KAM-GRI-1. Si hoy no las distinguís en el piso, numeralas igual: el sistema cuenta cuántas hay libres de cada modelo+familia.</t>
+          <t>Tiene que existir en la hoja Modelos.</t>
         </r>
       </text>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>Tiene que existir en la hoja Modelos.</t>
+          <t>Tiene que existir en la hoja Familias.</t>
         </r>
       </text>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
         <r>
-          <t>Tiene que existir en la hoja Familias.</t>
+          <t>El número que va grabado en la placa: MODELO · FAMILIA · NÚMERO. No se repite dentro del mismo modelo y familia. Si lo dejás vacío se asigna el siguiente.</t>
         </r>
       </text>
     </comment>
     <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>gris o blanco. Vacío = gris. Las de cemento blanco llevan los laterales pintados de blanco.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <t>Cuántos moldes tiene ESTE grupo. Puede variar entre estanterías del mismo producto (39, 38, 40).</t>
@@ -153,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="51">
   <si>
     <t>CONTROL DE ESTANTERIAS — plantilla de carga inicial</t>
   </si>
@@ -179,13 +193,16 @@
     <t>Modelo    = la forma de la pieza (Kamba, Uhma...). Define el molde.</t>
   </si>
   <si>
-    <t>Familia   = con qué se puede compartir molde. Dos tonos de beige comparten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            molde; un gris y un beige no, y cemento gris con cemento blanco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            tampoco. Es el criterio de compatibilidad, no el color exacto.</t>
+    <t>Familia   = el color: gris, beige, terracota... Dos tonos de beige comparten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            molde; un gris y un beige no.</t>
+  </si>
+  <si>
+    <t>Cemento   = gris o blanco. Tampoco se mezclan: para llenar una estantería,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            modelo, familia y cemento tienen que coincidir.</t>
   </si>
   <si>
     <t>Producto  = modelo x tono exacto. Es lo que se elige al llenar el trompo.</t>
@@ -194,7 +211,10 @@
     <t>Estanteria= un grupo fijo de moldes. Los 40 moldes de una estantería son</t>
   </si>
   <si>
-    <t xml:space="preserve">            siempre esos 40 y no se mezclan con los de otra.</t>
+    <t xml:space="preserve">            siempre esos 40 y no se mezclan con los de otra. Se identifica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            por su placa: MODELO · FAMILIA · NÚMERO.</t>
   </si>
   <si>
     <t>LAS DOS COLUMNAS QUE MAS SE PRESTAN A CONFUSION</t>
@@ -242,10 +262,10 @@
     <t>orden</t>
   </si>
   <si>
-    <t>Gris — cemento gris</t>
-  </si>
-  <si>
-    <t>Beige — cemento blanco</t>
+    <t>Gris</t>
+  </si>
+  <si>
+    <t>Beige</t>
   </si>
   <si>
     <t>Kamba</t>
@@ -269,6 +289,9 @@
     <t>pasa por tunel</t>
   </si>
   <si>
+    <t>cemento</t>
+  </si>
+  <si>
     <t>m2 por paquete</t>
   </si>
   <si>
@@ -278,37 +301,25 @@
     <t>si</t>
   </si>
   <si>
+    <t>gris</t>
+  </si>
+  <si>
     <t>Kamba Gris Basalto</t>
   </si>
   <si>
-    <t>Uhma Beige Arena</t>
-  </si>
-  <si>
-    <t>Uhma Beige Trigo</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>codigo</t>
+    <t>Uhma Beige</t>
+  </si>
+  <si>
+    <t>Uhma Beige Blanco</t>
+  </si>
+  <si>
+    <t>blanco</t>
+  </si>
+  <si>
+    <t>numero</t>
   </si>
   <si>
     <t>moldes</t>
-  </si>
-  <si>
-    <t>KAM-GRI-1</t>
-  </si>
-  <si>
-    <t>KAM-GRI-2</t>
-  </si>
-  <si>
-    <t>UHM-BEI-1</t>
-  </si>
-  <si>
-    <t>UHM-BEI-2</t>
-  </si>
-  <si>
-    <t>UHM-BEI-3</t>
   </si>
 </sst>
 </file>
@@ -713,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -801,21 +812,21 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -831,17 +842,17 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -851,21 +862,21 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
     </row>
@@ -877,6 +888,16 @@
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -896,15 +917,15 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -912,7 +933,7 @@
     </row>
     <row r="3" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
@@ -936,15 +957,15 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -952,7 +973,7 @@
     </row>
     <row r="3" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
@@ -967,7 +988,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -975,87 +996,98 @@
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="7" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1064,33 +1096,39 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="3">
+        <v>43</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.18</v>
+      <c r="G5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1102,95 +1140,114 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C3" s="3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="C6" s="3">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3">
         <v>40</v>
       </c>
     </row>
